--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>74.18599888545485</v>
+        <v>12.05522481888641</v>
       </c>
       <c r="D2" t="n">
-        <v>73.84160098351421</v>
+        <v>11.99926015982106</v>
       </c>
       <c r="E2" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F2" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>72.40311273770466</v>
+        <v>11.76550581987701</v>
       </c>
       <c r="D3" t="n">
-        <v>72.11536171452251</v>
+        <v>11.71874627860991</v>
       </c>
       <c r="E3" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F3" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.21705541573894</v>
+        <v>10.11027150505758</v>
       </c>
       <c r="D4" t="n">
-        <v>61.85225855837615</v>
+        <v>10.05099201573612</v>
       </c>
       <c r="E4" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F4" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>70.89949313777662</v>
+        <v>11.5211676348887</v>
       </c>
       <c r="D5" t="n">
-        <v>46.17899955607527</v>
+        <v>7.504087427862231</v>
       </c>
       <c r="E5" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F5" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.64381923211251</v>
+        <v>9.854620625218283</v>
       </c>
       <c r="D6" t="n">
-        <v>60.31017430337588</v>
+        <v>9.80040332429858</v>
       </c>
       <c r="E6" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F6" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.48766504492328</v>
+        <v>8.691745569800034</v>
       </c>
       <c r="D7" t="n">
-        <v>53.35843576297747</v>
+        <v>8.67074581148384</v>
       </c>
       <c r="E7" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F7" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.83118673077361</v>
+        <v>6.797567843750712</v>
       </c>
       <c r="D8" t="n">
-        <v>41.62216019798513</v>
+        <v>6.763601032172584</v>
       </c>
       <c r="E8" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F8" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.76824734843467</v>
+        <v>7.762340194120634</v>
       </c>
       <c r="D9" t="n">
-        <v>21.22809640193923</v>
+        <v>3.449565665315125</v>
       </c>
       <c r="E9" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F9" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.57397178467026</v>
+        <v>4.643270415008917</v>
       </c>
       <c r="D10" t="n">
-        <v>28.24573164670282</v>
+        <v>4.589931392589209</v>
       </c>
       <c r="E10" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F10" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>7.40327227193354</v>
+        <v>1.2030317441892</v>
       </c>
       <c r="D11" t="n">
-        <v>7.228991868620088</v>
+        <v>1.174711178650764</v>
       </c>
       <c r="E11" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F11" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>13.8371022278054</v>
+        <v>2.248529112018377</v>
       </c>
       <c r="D12" t="n">
-        <v>14.21294582195659</v>
+        <v>2.309603696067947</v>
       </c>
       <c r="E12" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F12" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.32522660801981</v>
+        <v>4.115349323803219</v>
       </c>
       <c r="D13" t="n">
-        <v>25.70545422361634</v>
+        <v>4.177136311337656</v>
       </c>
       <c r="E13" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F13" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>38.72475088921916</v>
+        <v>6.292772019498114</v>
       </c>
       <c r="D14" t="n">
-        <v>38.66729421348147</v>
+        <v>6.283435309690739</v>
       </c>
       <c r="E14" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F14" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>46.23873704858971</v>
+        <v>7.513794770395827</v>
       </c>
       <c r="D15" t="n">
-        <v>46.56765424816528</v>
+        <v>7.567243815326858</v>
       </c>
       <c r="E15" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F15" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.24290885485455</v>
+        <v>6.051972688913864</v>
       </c>
       <c r="D16" t="n">
-        <v>37.59778105508376</v>
+        <v>6.109639421451111</v>
       </c>
       <c r="E16" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F16" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>61.65017464950837</v>
+        <v>10.01815338054511</v>
       </c>
       <c r="D17" t="n">
-        <v>62.01688608894829</v>
+        <v>10.0777439894541</v>
       </c>
       <c r="E17" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F17" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>73.4212508608675</v>
+        <v>11.93095326489097</v>
       </c>
       <c r="D18" t="n">
-        <v>73.7900633620546</v>
+        <v>11.99088529633387</v>
       </c>
       <c r="E18" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F18" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>52.35956766624576</v>
+        <v>8.508429745764936</v>
       </c>
       <c r="D19" t="n">
-        <v>52.47911857710063</v>
+        <v>8.527856768778852</v>
       </c>
       <c r="E19" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F19" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>72.24370713072956</v>
+        <v>11.73960240874355</v>
       </c>
       <c r="D20" t="n">
-        <v>72.62718405641833</v>
+        <v>11.80191740916798</v>
       </c>
       <c r="E20" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F20" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>58.83752170098407</v>
+        <v>9.561097276409912</v>
       </c>
       <c r="D21" t="n">
-        <v>58.98395471749308</v>
+        <v>9.584892641592626</v>
       </c>
       <c r="E21" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F21" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>57.91746171066699</v>
+        <v>9.411587527983386</v>
       </c>
       <c r="D22" t="n">
-        <v>58.32393424146368</v>
+        <v>9.477639314237848</v>
       </c>
       <c r="E22" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F22" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>59.44994058836718</v>
+        <v>9.660615345609667</v>
       </c>
       <c r="D23" t="n">
-        <v>59.83808630163063</v>
+        <v>9.723689024014979</v>
       </c>
       <c r="E23" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F23" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>77.00012309111739</v>
+        <v>12.51252000230658</v>
       </c>
       <c r="D24" t="n">
-        <v>77.10627214584923</v>
+        <v>12.5297692237005</v>
       </c>
       <c r="E24" t="n">
-        <v>19.13918161004079</v>
+        <v>3.110117011631629</v>
       </c>
       <c r="F24" t="n">
-        <v>19.67582404972978</v>
+        <v>3.197321408081089</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
